--- a/signup_forms/026_gardening_workshop_series_lead_generation--signup_forms.xlsx
+++ b/signup_forms/026_gardening_workshop_series_lead_generation--signup_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Three</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Four</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Five</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Six</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Seven</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Eight</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Nine</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Ten</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Eleven</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gardening Workshop Series Lead Generation</t>
+          <t>Lead Generation Page Twelve</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
